--- a/quizzes/021_fragrance_recommendation_quiz--quizzes.xlsx
+++ b/quizzes/021_fragrance_recommendation_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>scent_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>What type of scent do you typically enjoy?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,20 +538,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>scent_type</t>
+          <t>family_size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_your_scent_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What size of fragrance family do you usually choose?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose 1-3 options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,17 +570,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>preferred_family</t>
+          <t>concentration_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_is_your_preferred_family</t>
+          <t>How concentrated would you like your fragrances to be?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Choose 2-3 options</t>
+          <t>Choose 1-2 options</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -588,47 +592,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>preferred_concentrate</t>
+          <t>wear_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_is_your_preferred_concentrate</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Choose 1-2 options</t>
-        </is>
-      </c>
+          <t>How long do you usually wear your fragrance?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear</t>
+          <t>after_activities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>When do you usually wear your fragrance after?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Choose 1-3 options</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -638,23 +642,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after</t>
+          <t>fragrance_usage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What will you be doing with the fragrance?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Choose 1-2 options</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,18 +674,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the purpose of the fragrance for you?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Choose 1 option</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,42 +701,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fragrance_purpose</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_is_the_purpose_of_fragrance</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you like to receive fragrance recommendations?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Choose 1 option</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_after</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_after</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Choose 1-2 options</t>
-        </is>
-      </c>
+          <t>Do you have any other preferences or information about your fragrance preferences?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -734,23 +746,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_would_you_like_to_recieve</t>
+          <t>special_occasion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>how_would_you_like_to_recieve</t>
+          <t>If you're planning to use the fragrance for a special occasion, what is it?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -762,12 +774,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>gift_recipient</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>If you're giving the fragrance as a gift, who is the recipient?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -785,315 +797,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Is there anything else you'd like to share about your preferences?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,10 +823,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1223,7 +936,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>preferred_family_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1240,7 +953,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>preferred_family_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1257,7 +970,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>preferred_family_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1274,7 +987,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>preferred_concentrate_choices</t>
+          <t>concentration_level_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1291,7 +1004,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>preferred_concentrate_choices</t>
+          <t>concentration_level_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1308,7 +1021,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>preferred_concentrate_choices</t>
+          <t>concentration_level_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1325,7 +1038,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_choices</t>
+          <t>wear_time_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1342,7 +1055,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_choices</t>
+          <t>wear_time_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1359,7 +1072,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_choices</t>
+          <t>wear_time_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1376,7 +1089,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_choices</t>
+          <t>wear_time_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,7 +1106,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_choices</t>
+          <t>wear_time_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1410,7 +1123,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after_choices</t>
+          <t>after_activities_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1427,7 +1140,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after_choices</t>
+          <t>after_activities_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1444,7 +1157,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after_choices</t>
+          <t>after_activities_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1461,7 +1174,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after_choices</t>
+          <t>after_activities_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1478,7 +1191,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>how_long_do_you_wear_after_choices</t>
+          <t>after_activities_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1495,7 +1208,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_choices</t>
+          <t>fragrance_usage_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1512,7 +1225,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_choices</t>
+          <t>fragrance_usage_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1529,7 +1242,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_choices</t>
+          <t>fragrance_usage_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1546,7 +1259,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_choices</t>
+          <t>fragrance_usage_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1563,7 +1276,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fragrance_purpose_choices</t>
+          <t>purpose_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1580,7 +1293,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fragrance_purpose_choices</t>
+          <t>purpose_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1597,117 +1310,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_after_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wearing</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wearing</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_after_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>giving_as_a_gift</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Giving as a gift</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>what_will_you_be_doing_with_fragrance_after_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>using_for_a_special_occasion</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Using for a special occasion</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>what_will_you_be_doing_with_fragrance_after_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>using_for_everyday</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Using for everyday</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>how_would_you_like_to_recieve_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>how_would_you_like_to_recieve_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>how_would_you_like_to_recieve_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>text_message</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>Text message</t>
         </is>
